--- a/new_input/commodity_idx.xlsx
+++ b/new_input/commodity_idx.xlsx
@@ -432,7 +432,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,7 +447,7 @@
         <v>珠子</v>
       </c>
       <c r="B2" t="str">
-        <v>木質</v>
+        <v>水晶</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         <v>珠子</v>
       </c>
       <c r="B3" t="str">
-        <v>水晶</v>
+        <v>珍珠</v>
       </c>
     </row>
     <row r="4">
@@ -463,7 +463,7 @@
         <v>珠子</v>
       </c>
       <c r="B4" t="str">
-        <v>珍珠</v>
+        <v>瑪瑙</v>
       </c>
     </row>
     <row r="5">
@@ -471,15 +471,15 @@
         <v>珠子</v>
       </c>
       <c r="B5" t="str">
-        <v>瑪瑙</v>
+        <v>礦石</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>珠子</v>
+        <v>配件</v>
       </c>
       <c r="B6" t="str">
-        <v>礦石</v>
+        <v>吊墜</v>
       </c>
     </row>
     <row r="7">
@@ -487,20 +487,12 @@
         <v>配件</v>
       </c>
       <c r="B7" t="str">
-        <v>吊墜</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>配件</v>
-      </c>
-      <c r="B8" t="str">
         <v>隔珠</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/new_input/commodity_idx.xlsx
+++ b/new_input/commodity_idx.xlsx
@@ -432,7 +432,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -487,12 +487,36 @@
         <v>配件</v>
       </c>
       <c r="B7" t="str">
+        <v>字母</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>配件</v>
+      </c>
+      <c r="B8" t="str">
+        <v>數字</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>配件</v>
+      </c>
+      <c r="B9" t="str">
+        <v>星座</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>配件</v>
+      </c>
+      <c r="B10" t="str">
         <v>隔珠</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/new_input/commodity_idx.xlsx
+++ b/new_input/commodity_idx.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,15 +417,21 @@
         <v>size_mm</v>
       </c>
       <c r="F1" t="str">
+        <v>high_mm</v>
+      </c>
+      <c r="G1" t="str">
         <v>price_twd</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>picture</v>
+      </c>
+      <c r="I1" t="str">
+        <v>supply</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/new_input/commodity_idx.xlsx
+++ b/new_input/commodity_idx.xlsx
@@ -438,7 +438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -509,7 +509,7 @@
         <v>配件</v>
       </c>
       <c r="B9" t="str">
-        <v>星座</v>
+        <v>方糖</v>
       </c>
     </row>
     <row r="10">
@@ -517,12 +517,28 @@
         <v>配件</v>
       </c>
       <c r="B10" t="str">
+        <v>星座</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>配件</v>
+      </c>
+      <c r="B11" t="str">
+        <v>跑環</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>配件</v>
+      </c>
+      <c r="B12" t="str">
         <v>隔珠</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
   </ignoredErrors>
 </worksheet>
 </file>